--- a/Luban/Config/Datas/Levels/L04/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L04/EnemyList.xlsx
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>10016905,10016910,10016907,10048500,10016909,10016908,10016905,10016910,10016907,10048500,10016909,10016908,10016905,10016910,10016907,10048500,10016909,10016908,10016905,10016910,10016907,10016902,10016909,10016908,10016905,10016910,10016907,10016902,10016909,10016908,10016905,10016910,10016907,10016902,10016909,10016911,10016905,10016910,10016907,10016902,10016909,10016911,10016905,10016910,10016907,10048501,10016914,10016911,10016905,10016910,10016907,10048501,10016914,10016911,10016905,10016910,10016913,10048501,10016914,10016911,10016905,10016910,10016913,10048501,10016914,10016912,10016905,10016910,10016913,10016903,10016914,10016912,10016905,10016910,10016913,10016903,10016914,10016912,10016905,10016910,10016913,10016903,10016914,10016912,10016905,10016910,10016913,10016904,10016914,10016912,10016905,10016910,10016913,10016904,10016915,10016905,10016910,10016913,10016904,10016915,10016905,10016910,10016913,10016904,10016915,10016905,10016910,10016915,10016906,10016910,10016915,10016906,10016910,10016915,10016906,10016910,10016915,10016906,10016910,10016915,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016910,10016910,10016910,10016910,10016910,10016910</t>
+          <t>10016905,10048500,10016907,10048500,10016909,10016908,10016905,10048500,10016907,10048500,10016909,10016908,10016905,10048500,10016907,10048500,10016909,10016908,10016905,10016902,10016907,10016902,10016909,10016908,10016905,10016902,10016907,10016902,10016909,10016908,10016905,10016902,10016907,10016902,10016909,10016911,10016905,10016902,10016907,10016902,10016909,10016911,10016905,10048501,10016907,10048501,10016914,10016911,10016905,10048501,10016907,10048501,10016914,10016911,10016905,10048501,10016913,10048501,10016914,10016911,10016905,10048501,10016913,10048501,10016914,10016912,10016905,10016903,10016913,10016903,10016914,10016912,10016905,10016903,10016913,10016903,10016914,10016912,10016905,10016903,10016913,10016903,10016914,10016912,10016905,10016904,10016913,10016904,10016914,10016912,10016905,10016904,10016913,10016904,10016915,10016905,10016904,10016913,10016904,10016915,10016905,10016904,10016913,10016904,10016915,10016905,10016910,10016915,10016906,10016910,10016915,10016906,10016910,10016915,10016906,10016910,10016915,10016906,10016910,10016915,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016906,10016910,10016910,10016910,10016910,10016910,10016910,10016910</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L4 W21/25; N=154; EHP=16226.000000; air:2x3,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x19,normal:18x18,fast:30x9,heavy:80x5,medium:83x7,swarm:84x43,heavy:86x5,heavy:88x5,fast:98x9,medium:108x8,medium:123x8</t>
+          <t>L4 W21/25; N=154; EHP=28737.144962; air:2x6,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x9,fast:98x9,heavy:80x5,heavy:86x5,heavy:88x5,medium:83x7,medium:108x8,medium:123x8,normal:17x19,normal:18x18,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>10016919,10016924,10016921,10048502,10016923,10016922,10016919,10016924,10016921,10048502,10016923,10016922,10016919,10016924,10016921,10048502,10016923,10016922,10016919,10016924,10016921,10048502,10016923,10016922,10016919,10016924,10016921,10016916,10016923,10016922,10016919,10016924,10016921,10016916,10016923,10016925,10016919,10016924,10016921,10016916,10016923,10016925,10016919,10016924,10016921,10048503,10016923,10016925,10016919,10016924,10016921,10048503,10016928,10016925,10016919,10016924,10016921,10048503,10016928,10016925,10016919,10016924,10016927,10048503,10016928,10016925,10016919,10016924,10016927,10016917,10016928,10016926,10016919,10016924,10016927,10016917,10016928,10016926,10016919,10016924,10016927,10016917,10016928,10016926,10016919,10016924,10016927,10016917,10016928,10016926,10016919,10016924,10016927,10016918,10016928,10016926,10016919,10016924,10016927,10016918,10016929,10016919,10016924,10016927,10016918,10016929,10016919,10016924,10016927,10016918,10016929,10016920,10016924,10016929,10016920,10016924,10016929,10016920,10016924,10016929,10016920,10016924,10016929,10016920,10016924,10016929,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016924,10016924,10016924,10016924,10016924,10016924</t>
+          <t>10016919,10048502,10016921,10048502,10016923,10016922,10016919,10048502,10016921,10048502,10016923,10016922,10016919,10048502,10016921,10048502,10016923,10016922,10016919,10048502,10016921,10048502,10016923,10016922,10016919,10016916,10016921,10016916,10016923,10016922,10016919,10016916,10016921,10016916,10016923,10016925,10016919,10016916,10016921,10016916,10016923,10016925,10016919,10048503,10016921,10048503,10016923,10016925,10016919,10048503,10016921,10048503,10016928,10016925,10016919,10048503,10016921,10048503,10016928,10016925,10016919,10048503,10016927,10048503,10016928,10016925,10016919,10016917,10016927,10016917,10016928,10016926,10016919,10016917,10016927,10016917,10016928,10016926,10016919,10016917,10016927,10016917,10016928,10016926,10016919,10016917,10016927,10016917,10016928,10016926,10016919,10016918,10016927,10016918,10016928,10016926,10016919,10016918,10016927,10016918,10016929,10016919,10016918,10016927,10016918,10016929,10016919,10016918,10016927,10016918,10016929,10016920,10016924,10016929,10016920,10016924,10016929,10016920,10016924,10016929,10016920,10016924,10016929,10016920,10016924,10016929,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016920,10016924,10016924,10016924,10016924,10016924,10016924,10016924</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L4 W22/25; N=160; EHP=16551.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x19,fast:30x10,heavy:80x5,medium:83x8,swarm:84x44,heavy:86x6,heavy:88x5,fast:98x9,medium:108x8,medium:123x8</t>
+          <t>L4 W22/25; N=160; EHP=29316.749724; air:2x8,air:11x6,air:12x8,air:13x8,air:14x8,fast:30x10,fast:98x9,heavy:80x5,heavy:86x6,heavy:88x5,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10016933,10016938,10016935,10048504,10016937,10016936,10016933,10016938,10016935,10048504,10016937,10016936,10016933,10016938,10016935,10048504,10016937,10016936,10016933,10016938,10016935,10048504,10016937,10016936,10016933,10016938,10016935,10016930,10016937,10016936,10016933,10016938,10016935,10016930,10016937,10016939,10016933,10016938,10016935,10016930,10016937,10016939,10016933,10016938,10016935,10016930,10016937,10016939,10016933,10016938,10016935,10048505,10016942,10016939,10016933,10016938,10016941,10048505,10016942,10016939,10016933,10016938,10016941,10048505,10016942,10016940,10016933,10016938,10016941,10048505,10016942,10016940,10016933,10016938,10016941,10016931,10016942,10016940,10016933,10016938,10016941,10016931,10016942,10016940,10016933,10016938,10016941,10016931,10016942,10016940,10016933,10016938,10016941,10016931,10016942,10016940,10016933,10016938,10016941,10016932,10016943,10016933,10016938,10016941,10016932,10016943,10016933,10016938,10016941,10016932,10016943,10016933,10016938,10016932,10016943,10016933,10016938,10016943,10016934,10016938,10016943,10016934,10016938,10016943,10016934,10016938,10016943,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016938,10016938,10016938,10016938,10016938</t>
+          <t>10016933,10048504,10016935,10048504,10016937,10016936,10016933,10048504,10016935,10048504,10016937,10016936,10016933,10048504,10016935,10048504,10016937,10016936,10016933,10048504,10016935,10048504,10016937,10016936,10016933,10016930,10016935,10016930,10016937,10016936,10016933,10016930,10016935,10016930,10016937,10016939,10016933,10016930,10016935,10016930,10016937,10016939,10016933,10016930,10016935,10016930,10016937,10016939,10016933,10048505,10016935,10048505,10016942,10016939,10016933,10048505,10016941,10048505,10016942,10016939,10016933,10048505,10016941,10048505,10016942,10016940,10016933,10048505,10016941,10048505,10016942,10016940,10016933,10016931,10016941,10016931,10016942,10016940,10016933,10016931,10016941,10016931,10016942,10016940,10016933,10016931,10016941,10016931,10016942,10016940,10016933,10016931,10016941,10016931,10016942,10016940,10016933,10016932,10016941,10016932,10016943,10016933,10016932,10016941,10016932,10016943,10016933,10016932,10016941,10016932,10016943,10016933,10016932,10016932,10016943,10016933,10016938,10016943,10016934,10016938,10016943,10016934,10016938,10016943,10016934,10016938,10016943,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016934,10016938,10016938,10016938,10016938,10016938,10016938</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L4 W23/25; N=166; EHP=16883.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x20,fast:30x9,heavy:80x5,medium:83x8,swarm:84x46,heavy:86x5,heavy:88x6,fast:98x10,medium:108x8,medium:123x8</t>
+          <t>L4 W23/25; N=166; EHP=29912.735735; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x9,fast:98x10,heavy:80x5,heavy:86x5,heavy:88x6,medium:83x8,medium:108x8,medium:123x8,normal:17x21,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10016947,10016952,10016949,10048506,10016951,10016950,10016947,10016952,10016949,10048506,10016951,10016950,10016947,10016952,10016949,10048506,10016951,10016950,10016947,10016952,10016949,10048506,10016951,10016950,10016947,10016952,10016949,10048506,10016951,10016950,10016947,10016952,10016949,10016944,10016951,10016950,10016947,10016952,10016949,10016944,10016951,10016953,10016947,10016952,10016949,10016944,10016951,10016953,10016947,10016952,10016949,10016944,10016956,10016953,10016947,10016952,10016949,10048507,10016956,10016953,10016947,10016952,10016955,10048507,10016956,10016953,10016947,10016952,10016955,10048507,10016956,10016953,10016947,10016952,10016955,10048507,10016956,10016954,10016947,10016952,10016955,10016945,10016956,10016954,10016947,10016952,10016955,10016945,10016956,10016954,10016947,10016952,10016955,10016945,10016956,10016954,10016947,10016952,10016955,10016945,10016957,10016954,10016947,10016952,10016955,10016946,10016957,10016947,10016952,10016955,10016946,10016957,10016947,10016952,10016955,10016946,10016957,10016948,10016952,10016946,10016957,10016948,10016952,10016957,10016948,10016952,10016957,10016948,10016952,10016957,10016948,10016952,10016957,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016952,10016952,10016952,10016952,10016952,10016952,10016952</t>
+          <t>10016947,10048506,10016949,10048506,10016951,10016950,10016947,10048506,10016949,10048506,10016951,10016950,10016947,10048506,10016949,10048506,10016951,10016950,10016947,10048506,10016949,10048506,10016951,10016950,10016947,10048506,10016949,10048506,10016951,10016950,10016947,10016944,10016949,10016944,10016951,10016950,10016947,10016944,10016949,10016944,10016951,10016953,10016947,10016944,10016949,10016944,10016951,10016953,10016947,10016944,10016949,10016944,10016956,10016953,10016947,10048507,10016949,10048507,10016956,10016953,10016947,10048507,10016955,10048507,10016956,10016953,10016947,10048507,10016955,10048507,10016956,10016953,10016947,10048507,10016955,10048507,10016956,10016954,10016947,10016945,10016955,10016945,10016956,10016954,10016947,10016945,10016955,10016945,10016956,10016954,10016947,10016945,10016955,10016945,10016956,10016954,10016947,10016945,10016955,10016945,10016957,10016954,10016947,10016946,10016955,10016946,10016957,10016947,10016946,10016955,10016946,10016957,10016947,10016946,10016955,10016946,10016957,10016948,10016946,10016946,10016957,10016948,10016952,10016957,10016948,10016952,10016957,10016948,10016952,10016957,10016948,10016952,10016957,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016948,10016952,10016952,10016952,10016952,10016952,10016952,10016952,10016952</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L4 W24/25; N=172; EHP=18078.000000; air:2x5,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x21,fast:30x10,heavy:80x6,medium:83x8,swarm:84x48,heavy:86x6,heavy:88x5,fast:98x10,medium:108x8,medium:123x9</t>
+          <t>L4 W24/25; N=172; EHP=32034.330839; air:2x10,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x10,fast:98x10,heavy:80x6,heavy:86x6,heavy:88x5,medium:83x8,medium:108x8,medium:123x9,normal:17x20,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10016961,10016966,10016963,10048508,10016965,10016964,10016971,10016961,10016966,10016963,10048508,10016965,10016964,10016961,10016966,10016963,10048508,10016965,10016964,10016961,10016966,10016963,10048508,10016965,10016964,10016961,10016966,10016963,10016958,10016965,10016964,10016961,10016966,10016963,10016958,10016965,10016967,10016961,10016966,10016963,10016958,10016965,10016967,10016961,10016966,10016963,10016958,10016965,10016967,10016961,10016966,10016963,10048509,10016965,10016967,10016961,10016966,10016963,10048509,10016970,10016967,10016961,10016966,10016969,10048509,10016970,10016967,10016961,10016966,10016969,10048509,10016970,10016968,10016961,10016966,10016969,10016959,10016970,10016968,10016961,10016966,10016969,10016959,10016970,10016968,10016961,10016966,10016969,10016959,10016970,10016968,10016961,10016966,10016969,10016959,10016970,10016968,10016961,10016966,10016969,10016959,10016970,10016968,10016961,10016966,10016969,10016960,10016970,10016961,10016966,10016969,10016960,10016972,10016961,10016966,10016969,10016960,10016972,10016961,10016966,10016969,10016960,10016972,10016961,10016966,10016972,10016962,10016966,10016972,10016962,10016966,10016972,10016962,10016966,10016972,10016962,10016966,10016972,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016966,10016966,10016966,10016966,10016966,10016966</t>
+          <t>10016961,10048508,10016963,10048508,10016965,10016964,10016971,10016961,10048508,10016963,10048508,10016965,10016964,10016961,10048508,10016963,10048508,10016965,10016964,10016961,10048508,10016963,10048508,10016965,10016964,10016961,10016958,10016963,10016958,10016965,10016964,10016961,10016958,10016963,10016958,10016965,10016967,10016961,10016958,10016963,10016958,10016965,10016967,10016961,10016958,10016963,10016958,10016965,10016967,10016961,10048509,10016963,10048509,10016965,10016967,10016961,10048509,10016963,10048509,10016970,10016967,10016961,10048509,10016969,10048509,10016970,10016967,10016961,10048509,10016969,10048509,10016970,10016968,10016961,10016959,10016969,10016959,10016970,10016968,10016961,10016959,10016969,10016959,10016970,10016968,10016961,10016959,10016969,10016959,10016970,10016968,10016961,10016959,10016969,10016959,10016970,10016968,10016961,10016959,10016969,10016959,10016970,10016968,10016961,10016960,10016969,10016960,10016970,10016961,10016960,10016969,10016960,10016972,10016961,10016960,10016969,10016960,10016972,10016961,10016960,10016969,10016960,10016972,10016961,10016966,10016972,10016962,10016966,10016972,10016962,10016966,10016972,10016962,10016966,10016972,10016962,10016966,10016972,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016962,10016966,10016966,10016966,10016966,10016966,10016966,10016966</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L4 W25/25; N=178; EHP=36090.000000; air:2x4,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x22,normal:18x21,fast:30x10,heavy:80x5,medium:83x9,swarm:84x49,heavy:86x6,heavy:88x6,fast:98x11,medium:108x9,elite:123x1,medium:123x8</t>
+          <t>L4 W25/25; N=178; EHP=63912.281058; air:2x8,air:11x8,air:12x8,air:13x10,air:14x8,elite:123x1,fast:30x10,fast:98x11,heavy:80x5,heavy:86x6,heavy:88x6,medium:83x9,medium:108x9,medium:123x8,normal:17x22,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L4 W1/25; N=34; EHP=191.488000; normal:17x17,normal:18x17</t>
+          <t>L4 W1/25; N=34; EHP=335.373487; normal:17x17,normal:18x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L4 W2/25; N=40; EHP=235.890688; normal:17x20,normal:18x20</t>
+          <t>L4 W2/25; N=40; EHP=413.140680; normal:17x20,normal:18x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3224136,3224673,3224019,3224136,3224673,3224091,3224136,3224673,3224099,3224136,3224673,3224099,3224136,3224673,3224107,3224136,3224673,3224115,3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224136,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144</t>
+          <t>3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224136,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224144,3224136,3224136,3224136,3224136,3224136,3224136</t>
         </is>
       </c>
       <c r="D11" s="0" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L4 W3/25; N=46; EHP=300.109005; air:2x1,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x14,normal:18x14,swarm:84x12</t>
+          <t>L4 W3/25; N=46; EHP=570.665663; normal:17x20,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3226136,3226673,3226019,3226136,3226673,3226019,3226136,3226673,3226091,3226136,3226673,3226099,3226136,3226673,3226107,3226136,3226673,3226115,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226136,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144</t>
+          <t>3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226136,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226144,3226136,3226136,3226136,3226136,3226136,3226136</t>
         </is>
       </c>
       <c r="D12" s="0" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L4 W4/25; N=52; EHP=390.651290; air:2x2,air:11x1,air:12x1,air:13x1,air:14x1,normal:17x16,normal:18x16,swarm:84x14</t>
+          <t>L4 W4/25; N=52; EHP=735.738059; normal:17x22,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3228136,3228673,3228019,3228668,3228136,3228673,3228091,3228668,3228136,3228673,3228091,3228668,3228136,3228673,3228099,3228868,3228136,3228673,3228107,3228868,3228136,3228673,3228107,3228988,3228136,3228673,3228115,3228988,3228136,3228673,3228988,3228136,3228673,3228136,3228673,3228136,3228673,3228136,3228673,3228136,3228673,3228136,3228673,3228144,3228673,3228144,3228673,3228144,3228144,3228144,3228144,3228144,3228144,3228144,3228144,3228144,3228144,3228144</t>
+          <t>3228136,3228019,3228019,3228668,3228136,3228091,3228091,3228668,3228136,3228091,3228091,3228668,3228136,3228099,3228099,3228868,3228136,3228107,3228107,3228868,3228136,3228107,3228107,3228988,3228136,3228115,3228115,3228988,3228136,3228673,3228988,3228136,3228673,3228136,3228673,3228136,3228673,3228136,3228673,3228136,3228673,3228136,3228673,3228144,3228673,3228144,3228673,3228144,3228144,3228144,3228144,3228144,3228144,3228144,3228144,3228144,3228144,3228144</t>
         </is>
       </c>
       <c r="D13" s="0" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L4 W5/25; N=58; EHP=750.477787; air:2x1,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x14,normal:18x13,medium:83x3,swarm:84x16,medium:108x2,medium:123x3</t>
+          <t>L4 W5/25; N=58; EHP=1331.383518; air:2x2,air:11x4,air:12x2,air:13x4,air:14x2,medium:83x3,medium:108x2,medium:123x3,normal:17x14,normal:18x13,swarm:84x9 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3230136,3230673,3230242,3230019,3230668,3230136,3230673,3230242,3230091,3230668,3230136,3230673,3230242,3230091,3230668,3230136,3230673,3230242,3230099,3230868,3230136,3230673,3230786,3230099,3230868,3230136,3230673,3230786,3230107,3230868,3230136,3230673,3230786,3230115,3230988,3230136,3230673,3230115,3230988,3230136,3230673,3230988,3230136,3230673,3230136,3230673,3230144,3230673,3230144,3230673,3230144,3230673,3230144,3230673,3230144,3230673,3230144,3230673,3230144,3230144,3230144,3230144,3230144,3230144</t>
+          <t>3230136,3230019,3230242,3230019,3230668,3230136,3230091,3230242,3230091,3230668,3230136,3230091,3230242,3230091,3230668,3230136,3230099,3230242,3230099,3230868,3230136,3230099,3230786,3230099,3230868,3230136,3230107,3230786,3230107,3230868,3230136,3230115,3230786,3230115,3230988,3230136,3230115,3230115,3230988,3230136,3230673,3230988,3230136,3230673,3230136,3230673,3230144,3230673,3230144,3230673,3230144,3230673,3230144,3230673,3230144,3230673,3230144,3230673,3230144,3230144,3230144,3230144,3230144,3230144</t>
         </is>
       </c>
       <c r="D14" s="0" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L4 W6/25; N=64; EHP=766.000000; air:2x1,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x11,normal:18x12,fast:30x4,medium:83x3,swarm:84x17,fast:98x3,medium:108x3,medium:123x3</t>
+          <t>L4 W6/25; N=64; EHP=1359.799788; air:2x2,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x4,fast:98x3,medium:83x3,medium:108x3,medium:123x3,normal:17x11,normal:18x12,swarm:84x9 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3232136,3232673,3232242,3232019,3232668,3232136,3232673,3232242,3232019,3232668,3232136,3232673,3232242,3232091,3232668,3232136,3232673,3232242,3232099,3232868,3232136,3232673,3232786,3232099,3232868,3232136,3232673,3232786,3232107,3232868,3232136,3232673,3232786,3232115,3232868,3232136,3232673,3232786,3232115,3232988,3232136,3232673,3232988,3232136,3232673,3232988,3232136,3232673,3232136,3232673,3232136,3232673,3232144,3232673,3232144,3232673,3232144,3232673,3232144,3232673,3232144,3232673,3232144,3232673,3232144,3232144,3232144,3232144,3232144,3232144</t>
+          <t>3232136,3232019,3232242,3232019,3232668,3232136,3232019,3232242,3232019,3232668,3232136,3232091,3232242,3232091,3232668,3232136,3232099,3232242,3232099,3232868,3232136,3232099,3232786,3232099,3232868,3232136,3232107,3232786,3232107,3232868,3232136,3232115,3232786,3232115,3232868,3232136,3232115,3232786,3232115,3232988,3232136,3232673,3232988,3232136,3232673,3232988,3232136,3232673,3232136,3232673,3232136,3232673,3232144,3232673,3232144,3232673,3232144,3232673,3232144,3232673,3232144,3232673,3232144,3232673,3232144,3232144,3232144,3232144,3232144,3232144</t>
         </is>
       </c>
       <c r="D15" s="0" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L4 W7/25; N=70; EHP=885.305344; air:2x2,air:11x1,air:12x2,air:13x1,air:14x2,normal:17x13,normal:18x12,fast:30x4,medium:83x3,swarm:84x19,fast:98x4,medium:108x4,medium:123x3</t>
+          <t>L4 W7/25; N=70; EHP=1569.687400; air:2x4,air:11x2,air:12x4,air:13x2,air:14x4,fast:30x4,fast:98x4,medium:83x3,medium:108x4,medium:123x3,normal:17x13,normal:18x12,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3234136,3234673,3234242,3234019,3234668,3234136,3234673,3234242,3234019,3234668,3234136,3234673,3234242,3234091,3234668,3234136,3234673,3234242,3234091,3234668,3234136,3234673,3234242,3234099,3234868,3234136,3234673,3234786,3234099,3234868,3234136,3234673,3234786,3234107,3234868,3234136,3234673,3234786,3234107,3234988,3234136,3234673,3234786,3234115,3234988,3234136,3234673,3234988,3234136,3234673,3234988,3234136,3234673,3234136,3234673,3234144,3234673,3234144,3234673,3234144,3234673,3234144,3234673,3234144,3234673,3234144,3234673,3234144,3234673,3234144,3234673,3234144,3234144,3234144,3234144,3234144</t>
+          <t>3234136,3234019,3234242,3234019,3234668,3234136,3234019,3234242,3234019,3234668,3234136,3234091,3234242,3234091,3234668,3234136,3234091,3234242,3234091,3234668,3234136,3234099,3234242,3234099,3234868,3234136,3234099,3234786,3234099,3234868,3234136,3234107,3234786,3234107,3234868,3234136,3234107,3234786,3234107,3234988,3234136,3234115,3234786,3234115,3234988,3234136,3234673,3234988,3234136,3234673,3234988,3234136,3234673,3234136,3234673,3234144,3234673,3234144,3234673,3234144,3234673,3234144,3234673,3234144,3234673,3234144,3234673,3234144,3234673,3234144,3234673,3234144,3234144,3234144,3234144,3234144</t>
         </is>
       </c>
       <c r="D16" s="0" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L4 W8/25; N=76; EHP=1146.226893; air:2x2,air:11x2,air:12x2,air:13x2,air:14x1,normal:17x13,normal:18x13,fast:30x5,medium:83x4,swarm:84x21,fast:98x4,medium:108x3,medium:123x4</t>
+          <t>L4 W8/25; N=76; EHP=2033.302604; air:2x4,air:11x4,air:12x4,air:13x4,air:14x2,fast:30x5,fast:98x4,medium:83x4,medium:108x3,medium:123x4,normal:17x13,normal:18x13,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3236136,3236673,3236242,3236019,3236668,3236136,3236673,3236242,3236019,3236668,3236136,3236673,3236242,3236091,3236668,3236136,3236673,3236242,3236091,3236668,3236136,3236673,3236786,3236099,3236868,3236136,3236673,3236786,3236099,3236868,3236136,3236673,3236786,3236107,3236868,3236136,3236673,3236786,3236107,3236868,3236136,3236673,3236786,3236115,3236988,3236136,3236673,3236115,3236988,3236136,3236673,3236988,3236136,3236673,3236988,3236136,3236673,3236136,3236673,3236136,3236673,3236144,3236673,3236144,3236673,3236144,3236673,3236144,3236673,3236144,3236673,3236144,3236673,3236144,3236673,3236144,3236144,3236144,3236144,3236144,3236144,3236144</t>
+          <t>3236136,3236019,3236242,3236019,3236668,3236136,3236019,3236242,3236019,3236668,3236136,3236091,3236242,3236091,3236668,3236136,3236091,3236242,3236091,3236668,3236136,3236099,3236786,3236099,3236868,3236136,3236099,3236786,3236099,3236868,3236136,3236107,3236786,3236107,3236868,3236136,3236107,3236786,3236107,3236868,3236136,3236115,3236786,3236115,3236988,3236136,3236115,3236115,3236988,3236136,3236673,3236988,3236136,3236673,3236988,3236136,3236673,3236136,3236673,3236136,3236673,3236144,3236673,3236144,3236673,3236144,3236673,3236144,3236673,3236144,3236673,3236144,3236673,3236144,3236673,3236144,3236144,3236144,3236144,3236144,3236144,3236144</t>
         </is>
       </c>
       <c r="D17" s="0" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L4 W9/25; N=82; EHP=1466.014106; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x14,fast:30x4,medium:83x4,swarm:84x22,fast:98x5,medium:108x4,medium:123x4</t>
+          <t>L4 W9/25; N=82; EHP=2601.438712; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x4,fast:98x5,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3238136,3238673,3238242,3238019,3238668,3238136,3238673,3238242,3238019,3238668,3238136,3238673,3238242,3238091,3238668,3238136,3238673,3238242,3238091,3238668,3238136,3238673,3238242,3238099,3238868,3238136,3238673,3238786,3238099,3238868,3238136,3238673,3238786,3238107,3238868,3238136,3238673,3238786,3238107,3238868,3238136,3238673,3238786,3238107,3238868,3238136,3238673,3238786,3238115,3238988,3238136,3238673,3238115,3238988,3238136,3238673,3238988,3238136,3238673,3238988,3238136,3238673,3238136,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238144,3238144,3238144,3238144,3238144</t>
+          <t>3238136,3238019,3238242,3238019,3238668,3238136,3238019,3238242,3238019,3238668,3238136,3238091,3238242,3238091,3238668,3238136,3238091,3238242,3238091,3238668,3238136,3238099,3238242,3238099,3238868,3238136,3238099,3238786,3238099,3238868,3238136,3238107,3238786,3238107,3238868,3238136,3238107,3238786,3238107,3238868,3238136,3238107,3238786,3238107,3238868,3238136,3238115,3238786,3238115,3238988,3238136,3238115,3238115,3238988,3238136,3238673,3238988,3238136,3238673,3238988,3238136,3238673,3238136,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238673,3238144,3238144,3238144,3238144,3238144,3238144</t>
         </is>
       </c>
       <c r="D18" s="0" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L4 W10/25; N=88; EHP=2708.000000; air:2x2,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x15,normal:18x15,fast:30x5,medium:83x4,swarm:84x24,fast:98x5,medium:108x5,medium:123x4</t>
+          <t>L4 W10/25; N=88; EHP=4807.100541; air:2x4,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x5,fast:98x5,medium:83x4,medium:108x5,medium:123x4,normal:17x15,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3240136,3240673,3240242,3240019,3240668,3240645,3240136,3240673,3240242,3240019,3240668,3240645,3240136,3240673,3240242,3240091,3240668,3240645,3240136,3240673,3240242,3240091,3240668,3240645,3240136,3240673,3240242,3240091,3240668,3240645,3240136,3240673,3240786,3240099,3240868,3240709,3240136,3240673,3240786,3240099,3240868,3240709,3240136,3240673,3240786,3240107,3240868,3240709,3240136,3240673,3240786,3240107,3240868,3240709,3240136,3240673,3240786,3240115,3240988,3240136,3240673,3240786,3240115,3240988,3240136,3240673,3240988,3240144,3240673,3240988,3240144,3240673,3240988,3240144,3240673,3240144,3240673,3240144,3240673,3240144,3240673,3240144,3240673,3240144,3240673,3240144,3240673,3240144,3240673,3240144,3240673,3240673,3240673,3240673</t>
+          <t>3240136,3240019,3240242,3240019,3240668,3240645,3240136,3240019,3240242,3240019,3240668,3240645,3240136,3240091,3240242,3240091,3240668,3240645,3240136,3240091,3240242,3240091,3240668,3240645,3240136,3240091,3240242,3240091,3240668,3240645,3240136,3240099,3240786,3240099,3240868,3240709,3240136,3240099,3240786,3240099,3240868,3240709,3240136,3240107,3240786,3240107,3240868,3240709,3240136,3240107,3240786,3240107,3240868,3240709,3240136,3240115,3240786,3240115,3240988,3240136,3240115,3240786,3240115,3240988,3240136,3240673,3240988,3240144,3240673,3240988,3240144,3240673,3240988,3240144,3240673,3240144,3240673,3240144,3240673,3240144,3240673,3240144,3240673,3240144,3240673,3240144,3240673,3240144,3240673,3240144,3240673,3240673,3240673,3240673</t>
         </is>
       </c>
       <c r="D19" s="0" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L4 W11/25; N=94; EHP=2763.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x2,normal:17x12,normal:18x11,fast:30x5,heavy:80x5,medium:83x5,swarm:84x26,heavy:88x4,fast:98x6,medium:108x4,medium:123x5</t>
+          <t>L4 W11/25; N=94; EHP=4893.566391; air:2x4,air:11x6,air:12x4,air:13x4,air:14x4,fast:30x5,fast:98x6,heavy:80x5,heavy:88x4,medium:83x5,medium:108x4,medium:123x5,normal:17x12,normal:18x11,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3242136,3242673,3242242,3242019,3242668,3242645,3242136,3242673,3242242,3242019,3242668,3242645,3242136,3242673,3242242,3242091,3242668,3242645,3242136,3242673,3242242,3242091,3242668,3242645,3242136,3242673,3242242,3242099,3242668,3242645,3242136,3242673,3242242,3242099,3242868,3242709,3242136,3242673,3242786,3242099,3242868,3242709,3242136,3242673,3242786,3242107,3242868,3242709,3242136,3242673,3242786,3242107,3242868,3242709,3242136,3242673,3242786,3242115,3242868,3242709,3242136,3242673,3242786,3242115,3242988,3242144,3242673,3242786,3242115,3242988,3242144,3242673,3242988,3242144,3242673,3242988,3242144,3242673,3242988,3242144,3242673,3242144,3242673,3242144,3242673,3242144,3242673,3242144,3242673,3242144,3242673,3242144,3242673,3242144,3242673,3242673,3242673,3242673,3242673,3242673</t>
+          <t>3242136,3242019,3242242,3242019,3242668,3242645,3242136,3242019,3242242,3242019,3242668,3242645,3242136,3242091,3242242,3242091,3242668,3242645,3242136,3242091,3242242,3242091,3242668,3242645,3242136,3242099,3242242,3242099,3242668,3242645,3242136,3242099,3242242,3242099,3242868,3242709,3242136,3242099,3242786,3242099,3242868,3242709,3242136,3242107,3242786,3242107,3242868,3242709,3242136,3242107,3242786,3242107,3242868,3242709,3242136,3242115,3242786,3242115,3242868,3242709,3242136,3242115,3242786,3242115,3242988,3242144,3242115,3242786,3242115,3242988,3242144,3242673,3242988,3242144,3242673,3242988,3242144,3242673,3242988,3242144,3242673,3242144,3242673,3242144,3242673,3242144,3242673,3242144,3242673,3242144,3242673,3242144,3242673,3242144,3242673,3242673,3242673,3242673,3242673,3242673</t>
         </is>
       </c>
       <c r="D20" s="0" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L4 W12/25; N=100; EHP=2860.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x11,normal:18x12,fast:30x6,heavy:80x5,medium:83x5,swarm:84x28,heavy:88x5,fast:98x6,medium:108x5,medium:123x5</t>
+          <t>L4 W12/25; N=100; EHP=5066.655166; air:2x4,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x6,fast:98x6,heavy:80x5,heavy:88x5,medium:83x5,medium:108x5,medium:123x5,normal:17x11,normal:18x12,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3244136,3244673,3244242,3244019,3244668,3244645,3244136,3244673,3244242,3244019,3244668,3244645,3244136,3244673,3244242,3244019,3244668,3244645,3244136,3244673,3244242,3244091,3244668,3244645,3244136,3244673,3244242,3244091,3244668,3244645,3244136,3244673,3244242,3244099,3244868,3244709,3244136,3244673,3244786,3244099,3244868,3244709,3244136,3244673,3244786,3244099,3244868,3244709,3244136,3244673,3244786,3244107,3244868,3244709,3244136,3244673,3244786,3244107,3244868,3244709,3244136,3244673,3244786,3244107,3244988,3244136,3244673,3244786,3244115,3244988,3244136,3244673,3244115,3244988,3244136,3244673,3244988,3244144,3244673,3244988,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244673,3244673</t>
+          <t>3244136,3244019,3244242,3244019,3244668,3244645,3244136,3244019,3244242,3244019,3244668,3244645,3244136,3244019,3244242,3244019,3244668,3244645,3244136,3244091,3244242,3244091,3244668,3244645,3244136,3244091,3244242,3244091,3244668,3244645,3244136,3244099,3244242,3244099,3244868,3244709,3244136,3244099,3244786,3244099,3244868,3244709,3244136,3244099,3244786,3244099,3244868,3244709,3244136,3244107,3244786,3244107,3244868,3244709,3244136,3244107,3244786,3244107,3244868,3244709,3244136,3244107,3244786,3244107,3244988,3244136,3244115,3244786,3244115,3244988,3244136,3244115,3244115,3244988,3244136,3244673,3244988,3244144,3244673,3244988,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244144,3244673,3244673,3244673</t>
         </is>
       </c>
       <c r="D21" s="0" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L4 W13/25; N=106; EHP=3490.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x2,normal:17x14,normal:18x13,fast:30x6,heavy:80x5,medium:83x5,swarm:84x29,heavy:88x5,fast:98x6,medium:108x5,medium:123x5</t>
+          <t>L4 W13/25; N=106; EHP=6185.045358; air:2x6,air:11x4,air:12x6,air:13x6,air:14x4,fast:30x6,fast:98x6,heavy:80x5,heavy:88x5,medium:83x5,medium:108x5,medium:123x5,normal:17x14,normal:18x13,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3246136,3246673,3246242,3246019,3246668,3246645,3246136,3246673,3246242,3246019,3246668,3246645,3246136,3246673,3246242,3246019,3246668,3246645,3246136,3246673,3246242,3246091,3246668,3246645,3246136,3246673,3246242,3246091,3246668,3246645,3246136,3246673,3246242,3246091,3246668,3246709,3246136,3246673,3246242,3246099,3246868,3246709,3246136,3246673,3246786,3246099,3246868,3246709,3246136,3246673,3246786,3246107,3246868,3246709,3246136,3246673,3246786,3246107,3246868,3246709,3246136,3246673,3246786,3246107,3246868,3246709,3246136,3246673,3246786,3246115,3246988,3246136,3246673,3246786,3246115,3246988,3246136,3246673,3246988,3246144,3246673,3246988,3246144,3246673,3246988,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246673,3246673,3246673</t>
+          <t>3246136,3246019,3246242,3246019,3246668,3246645,3246136,3246019,3246242,3246019,3246668,3246645,3246136,3246019,3246242,3246019,3246668,3246645,3246136,3246091,3246242,3246091,3246668,3246645,3246136,3246091,3246242,3246091,3246668,3246645,3246136,3246091,3246242,3246091,3246668,3246709,3246136,3246099,3246242,3246099,3246868,3246709,3246136,3246099,3246786,3246099,3246868,3246709,3246136,3246107,3246786,3246107,3246868,3246709,3246136,3246107,3246786,3246107,3246868,3246709,3246136,3246107,3246786,3246107,3246868,3246709,3246136,3246115,3246786,3246115,3246988,3246136,3246115,3246786,3246115,3246988,3246136,3246673,3246988,3246144,3246673,3246988,3246144,3246673,3246988,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246144,3246673,3246673,3246673,3246673</t>
         </is>
       </c>
       <c r="D22" s="0" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L4 W14/25; N=112; EHP=4213.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x14,normal:18x14,fast:30x7,heavy:80x5,medium:83x6,swarm:84x31,heavy:88x6,fast:98x6,medium:108x5,medium:123x5</t>
+          <t>L4 W14/25; N=112; EHP=7461.051627; air:2x6,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x7,fast:98x6,heavy:80x5,heavy:88x6,medium:83x6,medium:108x5,medium:123x5,normal:17x14,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3248136,3248673,3248242,3248019,3248668,3248645,3248136,3248673,3248242,3248019,3248668,3248645,3248136,3248673,3248242,3248091,3248668,3248645,3248136,3248673,3248242,3248091,3248668,3248645,3248136,3248673,3248242,3248091,3248668,3248693,3248136,3248673,3248242,3248099,3248868,3248693,3248136,3248673,3248242,3248099,3248868,3248693,3248136,3248673,3248786,3248099,3248868,3248693,3248136,3248673,3248786,3248107,3248868,3248709,3248136,3248673,3248786,3248107,3248868,3248709,3248136,3248673,3248786,3248107,3248868,3248709,3248136,3248673,3248786,3248115,3248988,3248136,3248673,3248786,3248115,3248988,3248136,3248673,3248786,3248115,3248988,3248136,3248673,3248988,3248144,3248673,3248988,3248144,3248673,3248988,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248673,3248673,3248673,3248673</t>
+          <t>3248136,3248019,3248242,3248019,3248668,3248645,3248136,3248019,3248242,3248019,3248668,3248645,3248136,3248091,3248242,3248091,3248668,3248645,3248136,3248091,3248242,3248091,3248668,3248645,3248136,3248091,3248242,3248091,3248668,3248693,3248136,3248099,3248242,3248099,3248868,3248693,3248136,3248099,3248242,3248099,3248868,3248693,3248136,3248099,3248786,3248099,3248868,3248693,3248136,3248107,3248786,3248107,3248868,3248709,3248136,3248107,3248786,3248107,3248868,3248709,3248136,3248107,3248786,3248107,3248868,3248709,3248136,3248115,3248786,3248115,3248988,3248136,3248115,3248786,3248115,3248988,3248136,3248115,3248786,3248115,3248988,3248136,3248673,3248988,3248144,3248673,3248988,3248144,3248673,3248988,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673,3248673,3248673,3248673,3248673</t>
         </is>
       </c>
       <c r="D23" s="0" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L4 W15/25; N=118; EHP=7353.000000; air:2x2,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x14,fast:30x7,heavy:80x4,medium:83x5,swarm:84x33,heavy:86x4,heavy:88x3,fast:98x7,medium:108x6,medium:123x6</t>
+          <t>L4 W15/25; N=118; EHP=13026.183006; air:2x4,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x7,fast:98x7,heavy:80x4,heavy:86x4,heavy:88x3,medium:83x5,medium:108x6,medium:123x6,normal:17x15,normal:18x14,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>3250136,3250673,3250242,3250019,3250668,3250645,3250136,3250673,3250242,3250019,3250668,3250645,3250136,3250673,3250242,3250019,3250668,3250645,3250136,3250673,3250242,3250091,3250668,3250645,3250136,3250673,3250242,3250091,3250668,3250693,3250136,3250673,3250242,3250091,3250668,3250693,3250136,3250673,3250242,3250099,3250868,3250693,3250136,3250673,3250786,3250099,3250868,3250693,3250136,3250673,3250786,3250099,3250868,3250709,3250136,3250673,3250786,3250107,3250868,3250709,3250136,3250673,3250786,3250107,3250868,3250709,3250136,3250673,3250786,3250107,3250868,3250709,3250136,3250673,3250786,3250115,3250988,3250136,3250673,3250786,3250115,3250988,3250136,3250673,3250115,3250988,3250144,3250673,3250988,3250144,3250673,3250988,3250144,3250673,3250988,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250673,3250673,3250673</t>
+          <t>3250136,3250019,3250242,3250019,3250668,3250645,3250136,3250019,3250242,3250019,3250668,3250645,3250136,3250019,3250242,3250019,3250668,3250645,3250136,3250091,3250242,3250091,3250668,3250645,3250136,3250091,3250242,3250091,3250668,3250693,3250136,3250091,3250242,3250091,3250668,3250693,3250136,3250099,3250242,3250099,3250868,3250693,3250136,3250099,3250786,3250099,3250868,3250693,3250136,3250099,3250786,3250099,3250868,3250709,3250136,3250107,3250786,3250107,3250868,3250709,3250136,3250107,3250786,3250107,3250868,3250709,3250136,3250107,3250786,3250107,3250868,3250709,3250136,3250115,3250786,3250115,3250988,3250136,3250115,3250786,3250115,3250988,3250136,3250115,3250115,3250988,3250144,3250673,3250988,3250144,3250673,3250988,3250144,3250673,3250988,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250144,3250673,3250673,3250673,3250673</t>
         </is>
       </c>
       <c r="D24" s="0" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L4 W16/25; N=124; EHP=7501.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x16,fast:30x7,heavy:80x4,medium:83x6,swarm:84x34,heavy:86x4,heavy:88x4,fast:98x7,medium:108x6,medium:123x6</t>
+          <t>L4 W16/25; N=124; EHP=13290.362381; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x7,fast:98x7,heavy:80x4,heavy:86x4,heavy:88x4,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x16,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>3252136,3252673,3252242,3252019,3252668,3252645,3252136,3252673,3252242,3252019,3252668,3252645,3252136,3252673,3252242,3252019,3252668,3252645,3252136,3252673,3252242,3252091,3252668,3252645,3252136,3252673,3252242,3252091,3252668,3252693,3252136,3252673,3252242,3252091,3252668,3252693,3252136,3252673,3252242,3252099,3252668,3252693,3252136,3252673,3252786,3252099,3252868,3252693,3252136,3252673,3252786,3252099,3252868,3252709,3252136,3252673,3252786,3252107,3252868,3252709,3252136,3252673,3252786,3252107,3252868,3252709,3252136,3252673,3252786,3252107,3252868,3252709,3252136,3252673,3252786,3252115,3252868,3252709,3252136,3252673,3252786,3252115,3252988,3252136,3252673,3252786,3252115,3252988,3252136,3252673,3252115,3252988,3252144,3252673,3252988,3252144,3252673,3252988,3252144,3252673,3252988,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252673,3252673,3252673,3252673,3252673</t>
+          <t>3252136,3252019,3252242,3252019,3252668,3252645,3252136,3252019,3252242,3252019,3252668,3252645,3252136,3252019,3252242,3252019,3252668,3252645,3252136,3252091,3252242,3252091,3252668,3252645,3252136,3252091,3252242,3252091,3252668,3252693,3252136,3252091,3252242,3252091,3252668,3252693,3252136,3252099,3252242,3252099,3252668,3252693,3252136,3252099,3252786,3252099,3252868,3252693,3252136,3252099,3252786,3252099,3252868,3252709,3252136,3252107,3252786,3252107,3252868,3252709,3252136,3252107,3252786,3252107,3252868,3252709,3252136,3252107,3252786,3252107,3252868,3252709,3252136,3252115,3252786,3252115,3252868,3252709,3252136,3252115,3252786,3252115,3252988,3252136,3252115,3252786,3252115,3252988,3252136,3252115,3252115,3252988,3252144,3252673,3252988,3252144,3252673,3252988,3252144,3252673,3252988,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252144,3252673,3252673,3252673,3252673,3252673,3252673</t>
         </is>
       </c>
       <c r="D25" s="0" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L4 W17/25; N=130; EHP=7652.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x4,normal:17x16,normal:18x15,fast:30x7,heavy:80x4,medium:83x7,swarm:84x36,heavy:86x4,heavy:88x5,fast:98x8,medium:108x6,medium:123x6</t>
+          <t>L4 W17/25; N=130; EHP=13560.311074; air:2x6,air:11x6,air:12x6,air:13x6,air:14x8,fast:30x7,fast:98x8,heavy:80x4,heavy:86x4,heavy:88x5,medium:83x7,medium:108x6,medium:123x6,normal:17x16,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>3254136,3254673,3254242,3254019,3254668,3254645,3254136,3254673,3254242,3254019,3254668,3254645,3254136,3254673,3254242,3254019,3254668,3254645,3254136,3254673,3254242,3254091,3254668,3254645,3254136,3254673,3254242,3254091,3254668,3254645,3254136,3254673,3254242,3254091,3254668,3254693,3254136,3254673,3254242,3254099,3254868,3254693,3254136,3254673,3254242,3254099,3254868,3254693,3254136,3254673,3254786,3254099,3254868,3254693,3254136,3254673,3254786,3254099,3254868,3254709,3254136,3254673,3254786,3254107,3254868,3254709,3254136,3254673,3254786,3254107,3254868,3254709,3254136,3254673,3254786,3254107,3254868,3254709,3254136,3254673,3254786,3254115,3254988,3254136,3254673,3254786,3254115,3254988,3254136,3254673,3254786,3254115,3254988,3254144,3254673,3254988,3254144,3254673,3254988,3254144,3254673,3254988,3254144,3254673,3254988,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254673,3254673,3254673,3254673,3254673</t>
+          <t>3254136,3254019,3254242,3254019,3254668,3254645,3254136,3254019,3254242,3254019,3254668,3254645,3254136,3254019,3254242,3254019,3254668,3254645,3254136,3254091,3254242,3254091,3254668,3254645,3254136,3254091,3254242,3254091,3254668,3254645,3254136,3254091,3254242,3254091,3254668,3254693,3254136,3254099,3254242,3254099,3254868,3254693,3254136,3254099,3254242,3254099,3254868,3254693,3254136,3254099,3254786,3254099,3254868,3254693,3254136,3254099,3254786,3254099,3254868,3254709,3254136,3254107,3254786,3254107,3254868,3254709,3254136,3254107,3254786,3254107,3254868,3254709,3254136,3254107,3254786,3254107,3254868,3254709,3254136,3254115,3254786,3254115,3254988,3254136,3254115,3254786,3254115,3254988,3254136,3254115,3254786,3254115,3254988,3254144,3254673,3254988,3254144,3254673,3254988,3254144,3254673,3254988,3254144,3254673,3254988,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254673,3254673,3254673,3254673,3254673,3254673</t>
         </is>
       </c>
       <c r="D26" s="0" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L4 W18/25; N=136; EHP=8178.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x16,normal:18x17,fast:30x8,heavy:80x5,medium:83x6,swarm:84x38,heavy:86x4,heavy:88x4,fast:98x8,medium:108x7,medium:123x7</t>
+          <t>L4 W18/25; N=136; EHP=14485.424559; air:2x6,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x8,fast:98x8,heavy:80x5,heavy:86x4,heavy:88x4,medium:83x6,medium:108x7,medium:123x7,normal:17x16,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>3256136,3256673,3256242,3256019,3256668,3256645,3256136,3256673,3256242,3256019,3256668,3256645,3256136,3256673,3256242,3256019,3256668,3256645,3256136,3256673,3256242,3256019,3256668,3256645,3256136,3256673,3256242,3256091,3256668,3256693,3256136,3256673,3256242,3256091,3256668,3256693,3256136,3256673,3256242,3256091,3256668,3256693,3256136,3256673,3256242,3256099,3256868,3256693,3256136,3256673,3256786,3256099,3256868,3256693,3256136,3256673,3256786,3256099,3256868,3256709,3256136,3256673,3256786,3256107,3256868,3256709,3256136,3256673,3256786,3256107,3256868,3256709,3256136,3256673,3256786,3256107,3256868,3256709,3256136,3256673,3256786,3256107,3256868,3256709,3256136,3256673,3256786,3256115,3256988,3256136,3256673,3256786,3256115,3256988,3256136,3256673,3256786,3256115,3256988,3256144,3256673,3256988,3256144,3256673,3256988,3256144,3256673,3256988,3256144,3256673,3256988,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256673,3256673,3256673,3256673,3256673</t>
+          <t>3256136,3256019,3256242,3256019,3256668,3256645,3256136,3256019,3256242,3256019,3256668,3256645,3256136,3256019,3256242,3256019,3256668,3256645,3256136,3256019,3256242,3256019,3256668,3256645,3256136,3256091,3256242,3256091,3256668,3256693,3256136,3256091,3256242,3256091,3256668,3256693,3256136,3256091,3256242,3256091,3256668,3256693,3256136,3256099,3256242,3256099,3256868,3256693,3256136,3256099,3256786,3256099,3256868,3256693,3256136,3256099,3256786,3256099,3256868,3256709,3256136,3256107,3256786,3256107,3256868,3256709,3256136,3256107,3256786,3256107,3256868,3256709,3256136,3256107,3256786,3256107,3256868,3256709,3256136,3256107,3256786,3256107,3256868,3256709,3256136,3256115,3256786,3256115,3256988,3256136,3256115,3256786,3256115,3256988,3256136,3256115,3256786,3256115,3256988,3256144,3256673,3256988,3256144,3256673,3256988,3256144,3256673,3256988,3256144,3256673,3256988,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256673,3256673,3256673,3256673,3256673</t>
         </is>
       </c>
       <c r="D27" s="0" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L4 W19/25; N=142; EHP=9470.000000; air:2x4,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x17,normal:18x17,fast:30x8,heavy:80x4,medium:83x7,swarm:84x39,heavy:86x5,heavy:88x5,fast:98x9,medium:108x7,medium:123x7</t>
+          <t>L4 W19/25; N=142; EHP=16776.404685; air:2x8,air:11x6,air:12x6,air:13x8,air:14x6,fast:30x8,fast:98x9,heavy:80x4,heavy:86x5,heavy:88x5,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>3258136,3258673,3258242,3258019,3258668,3258645,3258136,3258673,3258242,3258019,3258668,3258645,3258136,3258673,3258242,3258019,3258668,3258645,3258136,3258673,3258242,3258091,3258668,3258645,3258136,3258673,3258242,3258091,3258668,3258645,3258136,3258673,3258242,3258091,3258668,3258693,3258136,3258673,3258242,3258091,3258668,3258693,3258136,3258673,3258242,3258099,3258668,3258693,3258136,3258673,3258242,3258099,3258868,3258693,3258136,3258673,3258786,3258099,3258868,3258709,3258136,3258673,3258786,3258107,3258868,3258709,3258136,3258673,3258786,3258107,3258868,3258709,3258136,3258673,3258786,3258107,3258868,3258709,3258136,3258673,3258786,3258107,3258868,3258709,3258136,3258673,3258786,3258115,3258868,3258136,3258673,3258786,3258115,3258988,3258136,3258673,3258786,3258115,3258988,3258136,3258673,3258115,3258988,3258144,3258673,3258988,3258144,3258673,3258988,3258144,3258673,3258988,3258144,3258673,3258988,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258673,3258673,3258673,3258673,3258673</t>
+          <t>3258136,3258019,3258242,3258019,3258668,3258645,3258136,3258019,3258242,3258019,3258668,3258645,3258136,3258019,3258242,3258019,3258668,3258645,3258136,3258091,3258242,3258091,3258668,3258645,3258136,3258091,3258242,3258091,3258668,3258645,3258136,3258091,3258242,3258091,3258668,3258693,3258136,3258091,3258242,3258091,3258668,3258693,3258136,3258099,3258242,3258099,3258668,3258693,3258136,3258099,3258242,3258099,3258868,3258693,3258136,3258099,3258786,3258099,3258868,3258709,3258136,3258107,3258786,3258107,3258868,3258709,3258136,3258107,3258786,3258107,3258868,3258709,3258136,3258107,3258786,3258107,3258868,3258709,3258136,3258107,3258786,3258107,3258868,3258709,3258136,3258115,3258786,3258115,3258868,3258136,3258115,3258786,3258115,3258988,3258136,3258115,3258786,3258115,3258988,3258136,3258115,3258115,3258988,3258144,3258673,3258988,3258144,3258673,3258988,3258144,3258673,3258988,3258144,3258673,3258988,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673,3258673,3258673,3258673,3258673,3258673</t>
         </is>
       </c>
       <c r="D28" s="0" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L4 W20/25; N=148; EHP=15907.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x18,normal:18x18,fast:30x9,heavy:80x5,medium:83x8,swarm:84x41,heavy:86x4,heavy:88x5,fast:98x8,medium:108x7,medium:123x7</t>
+          <t>L4 W20/25; N=148; EHP=28186.542176; air:2x6,air:11x8,air:12x6,air:13x8,air:14x8,fast:30x9,fast:98x8,heavy:80x5,heavy:86x4,heavy:88x5,medium:83x8,medium:108x7,medium:123x7,normal:17x18,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L04/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L04/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>134</v>
+        <v>300</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>128</v>
+        <v>260</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>128</v>
+        <v>340</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>253</v>
+        <v>330</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>239</v>
+        <v>310</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>211</v>
+        <v>320</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>204</v>
+        <v>250</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>197</v>
+        <v>280</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>169</v>
+        <v>330</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>162</v>
+        <v>250</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>155</v>
+        <v>230</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
